--- a/fullanime.xlsx
+++ b/fullanime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VoVanLinhTinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23835C8-8EFE-439E-8C40-11CF4BA8A1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D6CF35-2A46-449A-ACC5-54964469534C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="212">
   <si>
     <t>Netoge no Yome ga Ninki Idol datta</t>
   </si>
@@ -700,10 +700,6 @@
 偽物語</t>
   </si>
   <si>
-    <t>Durarara
-デュラララ</t>
-  </si>
-  <si>
     <t>Danganronpa: Kibou no Gakuen to Zetsubou no Koukousei The Animation
 ダンガンロンパ 希望の学園と絶望の高校生 THE ANIMATION
 Danganronpa: Học viện Hy vọng và Học sinh của Tuyệt vọng – The Animation</t>
@@ -1043,6 +1039,25 @@
     <t>Steins;Gate Movie: Fuka Ryouiki no Déjà vu
 劇場版 STEINS;GATE 負荷領域のデジャヴ
 STEINS;GATE: Bản điện ảnh – Déjà vu của miền chịu tải</t>
+  </si>
+  <si>
+    <t>Durarara
+デュラララ
+Durarara</t>
+  </si>
+  <si>
+    <t>Otome Kaijuu Caraméliser
+乙女怪獣キャラメリゼ</t>
+  </si>
+  <si>
+    <t>Vanitas no Karte
+ヴァニタスの手記
+Hồi ký về Vanitas</t>
+  </si>
+  <si>
+    <t>Fruits Basket
+フルーツバスケット
+Giỏ trái cây</t>
   </si>
 </sst>
 </file>
@@ -1713,19 +1728,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>184</v>
-      </c>
       <c r="E1" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="50.4" x14ac:dyDescent="0.3">
@@ -1977,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E16" s="14">
         <v>2013</v>
@@ -2608,8 +2623,8 @@
       </c>
       <c r="E55" s="14"/>
     </row>
-    <row r="56" spans="1:5" ht="50.4" x14ac:dyDescent="0.35">
-      <c r="A56" s="15">
+    <row r="56" spans="1:5" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="12">
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
@@ -2619,7 +2634,7 @@
         <v>66</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E56" s="14"/>
     </row>
@@ -2829,7 +2844,7 @@
         <v>66</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E70" s="14"/>
     </row>
@@ -2844,7 +2859,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E71" s="14"/>
     </row>
@@ -2874,7 +2889,7 @@
         <v>66</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E73" s="14"/>
     </row>
@@ -2919,7 +2934,7 @@
         <v>66</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E76" s="14"/>
     </row>
@@ -3009,7 +3024,7 @@
         <v>66</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E82" s="14">
         <v>2006</v>
@@ -3116,7 +3131,7 @@
         <v>66</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E89" s="14">
         <v>2019</v>
@@ -3148,7 +3163,7 @@
         <v>66</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E91" s="14"/>
     </row>
@@ -3478,7 +3493,7 @@
         <v>66</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E113" s="14">
         <v>2013</v>
@@ -3754,8 +3769,8 @@
       </c>
       <c r="E131" s="14"/>
     </row>
-    <row r="132" spans="1:5" ht="33.6" x14ac:dyDescent="0.35">
-      <c r="A132" s="15">
+    <row r="132" spans="1:5" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A132" s="12">
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
@@ -3765,9 +3780,11 @@
         <v>2</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E132" s="14"/>
+        <v>208</v>
+      </c>
+      <c r="E132" s="14">
+        <v>2004</v>
+      </c>
     </row>
     <row r="133" spans="1:5" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="15">
@@ -3780,7 +3797,7 @@
         <v>66</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E133" s="14"/>
     </row>
@@ -3975,7 +3992,7 @@
         <v>2</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E146" s="14"/>
     </row>
@@ -3990,7 +4007,7 @@
         <v>66</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E147" s="14"/>
     </row>
@@ -4005,7 +4022,7 @@
         <v>66</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E148" s="14"/>
     </row>
@@ -4020,7 +4037,7 @@
         <v>66</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E149" s="14"/>
     </row>
@@ -4035,7 +4052,7 @@
         <v>66</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E150" s="14"/>
     </row>
@@ -4050,7 +4067,7 @@
         <v>66</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E151" s="14"/>
     </row>
@@ -4065,7 +4082,7 @@
         <v>66</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E152" s="14"/>
     </row>
@@ -4080,7 +4097,7 @@
         <v>66</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E153" s="14"/>
     </row>
@@ -4095,7 +4112,7 @@
         <v>66</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E154" s="14"/>
     </row>
@@ -4110,7 +4127,7 @@
         <v>66</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E155" s="14"/>
     </row>
@@ -4125,7 +4142,7 @@
         <v>66</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E156" s="14"/>
     </row>
@@ -4140,7 +4157,7 @@
         <v>66</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E157" s="14"/>
     </row>
@@ -4155,7 +4172,7 @@
         <v>66</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E158" s="14"/>
     </row>
@@ -4170,7 +4187,7 @@
         <v>66</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E159" s="14"/>
     </row>
@@ -4185,7 +4202,7 @@
         <v>66</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E160" s="14"/>
     </row>
@@ -4200,7 +4217,7 @@
         <v>66</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E161" s="14"/>
     </row>
@@ -4215,7 +4232,7 @@
         <v>66</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E162" s="14"/>
     </row>
@@ -4230,7 +4247,7 @@
         <v>66</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E163" s="14"/>
     </row>
@@ -4245,7 +4262,7 @@
         <v>66</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E164" s="14"/>
     </row>
@@ -4260,7 +4277,7 @@
         <v>66</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E165" s="14"/>
     </row>
@@ -4275,7 +4292,7 @@
         <v>66</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E166" s="14"/>
     </row>
@@ -4290,7 +4307,7 @@
         <v>66</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E167" s="14"/>
     </row>
@@ -4305,7 +4322,7 @@
         <v>66</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E168" s="14"/>
     </row>
@@ -4320,7 +4337,7 @@
         <v>66</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E169" s="14"/>
     </row>
@@ -4335,7 +4352,7 @@
         <v>66</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E170" s="14"/>
     </row>
@@ -4350,7 +4367,7 @@
         <v>2</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E171" s="14"/>
     </row>
@@ -4365,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E172" s="14"/>
     </row>
@@ -4380,7 +4397,7 @@
         <v>2</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E173" s="14"/>
     </row>
@@ -4395,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E174" s="14"/>
     </row>
@@ -4410,7 +4427,7 @@
         <v>2</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E175" s="14"/>
     </row>
@@ -4425,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E176" s="14"/>
     </row>
@@ -4440,7 +4457,7 @@
         <v>2</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E177" s="14"/>
     </row>
@@ -4455,7 +4472,7 @@
         <v>2</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E178" s="14"/>
     </row>
@@ -4485,7 +4502,7 @@
         <v>2</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E180" s="14"/>
     </row>
@@ -4500,7 +4517,7 @@
         <v>1</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E181" s="14"/>
     </row>
@@ -4515,7 +4532,7 @@
         <v>2</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E182" s="14"/>
     </row>
@@ -4530,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E183" s="14"/>
     </row>
@@ -4545,7 +4562,7 @@
         <v>2</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E184" s="14"/>
     </row>
@@ -4560,7 +4577,7 @@
         <v>2</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E185" s="14"/>
     </row>
@@ -4575,7 +4592,7 @@
         <v>2</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E186" s="14"/>
     </row>
@@ -4590,7 +4607,7 @@
         <v>2</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E187" s="14"/>
     </row>
@@ -4605,7 +4622,7 @@
         <v>2</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E188" s="14"/>
     </row>
@@ -4620,7 +4637,7 @@
         <v>66</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E189" s="14"/>
     </row>
@@ -4635,7 +4652,7 @@
         <v>2</v>
       </c>
       <c r="D190" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E190" s="14"/>
     </row>
@@ -4650,7 +4667,7 @@
         <v>66</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E191" s="14"/>
     </row>
@@ -4665,7 +4682,7 @@
         <v>2</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E192" s="14"/>
     </row>
@@ -4680,7 +4697,7 @@
         <v>66</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E193" s="14"/>
     </row>
@@ -4695,7 +4712,7 @@
         <v>66</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E194" s="14"/>
     </row>
@@ -4710,7 +4727,7 @@
         <v>66</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E195" s="14"/>
     </row>
@@ -4725,7 +4742,7 @@
         <v>66</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E196" s="14"/>
     </row>
@@ -4740,7 +4757,7 @@
         <v>66</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E197" s="14"/>
     </row>
@@ -4755,7 +4772,7 @@
         <v>66</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E198" s="14"/>
     </row>
@@ -4770,7 +4787,7 @@
         <v>66</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E199" s="14"/>
     </row>
@@ -4785,7 +4802,7 @@
         <v>66</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E200" s="14"/>
     </row>
@@ -4800,7 +4817,7 @@
         <v>2</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E201" s="14"/>
     </row>
@@ -4815,7 +4832,7 @@
         <v>66</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E202" s="14"/>
     </row>
@@ -4830,41 +4847,49 @@
         <v>66</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E203" s="14"/>
     </row>
-    <row r="204" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A204" s="15"/>
+    <row r="204" spans="1:5" ht="50.4" x14ac:dyDescent="0.35">
+      <c r="A204" s="15">
+        <v>203</v>
+      </c>
       <c r="B204" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C204" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D204" s="8"/>
+      <c r="D204" s="7" t="s">
+        <v>210</v>
+      </c>
       <c r="E204" s="14"/>
     </row>
-    <row r="205" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" ht="33.6" x14ac:dyDescent="0.35">
       <c r="A205" s="15"/>
       <c r="B205" s="11" t="s">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D205" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>209</v>
+      </c>
       <c r="E205" s="14"/>
     </row>
-    <row r="206" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" ht="50.4" x14ac:dyDescent="0.35">
       <c r="A206" s="15"/>
       <c r="B206" s="11" t="s">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D206" s="8"/>
+      <c r="D206" s="7" t="s">
+        <v>211</v>
+      </c>
       <c r="E206" s="14"/>
     </row>
     <row r="207" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.35">
@@ -8111,9 +8136,11 @@
     <hyperlink ref="A34" r:id="rId33" display="https://myanimelist.net/anime/10014/Shouwa_Monogatari" xr:uid="{EEC84E08-86BD-47F1-BD77-7208E3105983}"/>
     <hyperlink ref="A35" r:id="rId34" display="https://myanimelist.net/anime/47257/Shinigami_Bocchan_to_Kuro_Maid" xr:uid="{02BEA18F-D968-4930-9502-4E7AF23CF021}"/>
     <hyperlink ref="A36" r:id="rId35" display="https://myanimelist.net/anime/1033/Sennen_Joyuu" xr:uid="{8A4E8A4F-FDB3-4727-BF83-072F9455DEA6}"/>
+    <hyperlink ref="A132" r:id="rId36" display="https://myanimelist.net/anime/6746/Durarara" xr:uid="{BE8B1CB9-F6F5-46F5-B3D4-0D0F9C6605F9}"/>
+    <hyperlink ref="A56" r:id="rId37" display="https://myanimelist.net/anime/2167/Clannad" xr:uid="{73E00FFB-23FB-4B54-B47D-FC3E0095C12B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId36"/>
-  <drawing r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId38"/>
+  <drawing r:id="rId39"/>
 </worksheet>
 </file>
--- a/fullanime.xlsx
+++ b/fullanime.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VoVanLinhTinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635160B4-CC82-492F-ACFF-8972D762DD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65523C51-A729-4547-A8AA-94675AE2D9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="250">
   <si>
     <t>Netoge no Yome ga Ninki Idol datta</t>
   </si>
@@ -1162,6 +1162,71 @@
     <t>Neko to Ryuu
 猫と竜
 Mèo và Rồng</t>
+  </si>
+  <si>
+    <t>Gosick
+ゴシック
+Gosick</t>
+  </si>
+  <si>
+    <t>Bukiyou na Senpai
+不器用な先輩
+Senpai vụng về</t>
+  </si>
+  <si>
+    <t>Giji Harem
+疑似ハーレム
+Hậu cung giả tạo</t>
+  </si>
+  <si>
+    <t>Kawaii dake ja Nai Shikimori-san
+可愛いだけじゃない式守さん
+Shikimori không chỉ dễ thương</t>
+  </si>
+  <si>
+    <t>Keikenzumi na Kimi to, Keiken Zero na Ore ga, Otsukiai suru Hanashi.
+経験済みなキミと、 経験ゼロなオレが、 お付き合いする話。
+Câu chuyện về tôi, một người chưa từng có kinh nghiệm, hẹn hò với cậu, người đã có kinh nghiệm.</t>
+  </si>
+  <si>
+    <t>Shuumatsu Nani Shitemasu ka? Isogashii desu ka? Sukutte Moratte Ii desu ka?
+終末なにしてますか？忙しいですか？救ってもらっていいですか？
+Cậu đang làm gì ở cuối vậy? Cậu bận à? Cậu có thể cứu tớ không?</t>
+  </si>
+  <si>
+    <t>Lv2 kara Cheat datta Motoyuusha Kouho no Mattari Isekai Life
+Lv2からチートだった元勇者候補のまったり異世界ライフ
+Thư giãn ở một thế giới khác với sức mạnh siêu gian lận cấp độ 2</t>
+  </si>
+  <si>
+    <t>Kami no Niwatsuki Kusunoki-tei
+神の庭付き楠木邸
+Khu nhà ở Kusunoki với khu vườn của Thượng Đế</t>
+  </si>
+  <si>
+    <t>Koori Zokusei Danshi to Cool na Douryou Joshi
+氷属性男子とクールな同僚女子
+Chàng Băng Giá Và Nàng Lạnh Lùng</t>
+  </si>
+  <si>
+    <t>Shinchou Yuusha: Kono Yuusha ga Ore Tsueee Kuse ni Shinchou Sugiru
+慎重勇者 ～この勇者が俺TUEEEくせに慎重すぎる～
+Anh hùng thận trọng: Anh hùng sở hữu sức mạnh vượt trội nhưng lại quá thận trọng.</t>
+  </si>
+  <si>
+    <t>Ao no Orchestra
+青のオーケストラ
+Dàn nhạc Xanh</t>
+  </si>
+  <si>
+    <t>Black Clover
+ブラッククローバー
+Cỏ ba lá đen</t>
+  </si>
+  <si>
+    <t>Nijusseiki Denki Mokuroku
+二十世紀電氣目録
+Danh mục thiết bị điện thế kỷ 20</t>
   </si>
 </sst>
 </file>
@@ -4182,7 +4247,7 @@
     </row>
     <row r="182" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B182" s="8" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>65</v>
@@ -4190,7 +4255,9 @@
       <c r="D182" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="E182" s="9"/>
+      <c r="E182" s="12">
+        <v>2012</v>
+      </c>
     </row>
     <row r="183" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B183" s="8" t="s">
@@ -4728,135 +4795,187 @@
       </c>
       <c r="E224" s="9"/>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B225" s="8" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C225" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D225" s="4"/>
-      <c r="E225" s="9"/>
-    </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D225" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E225" s="12">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B226" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C226" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D226" s="4"/>
-      <c r="E226" s="9"/>
-    </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D226" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E226" s="12">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B227" s="8" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C227" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D227" s="4"/>
-      <c r="E227" s="9"/>
-    </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D227" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E227" s="12">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B228" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C228" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D228" s="4"/>
-      <c r="E228" s="9"/>
-    </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D228" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E228" s="12">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" ht="67.2" x14ac:dyDescent="0.3">
       <c r="B229" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D229" s="4"/>
-      <c r="E229" s="9"/>
-    </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D229" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E229" s="12">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B230" s="8" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C230" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D230" s="4"/>
-      <c r="E230" s="9"/>
-    </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D230" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E230" s="12">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="231" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B231" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D231" s="4"/>
-      <c r="E231" s="9"/>
-    </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D231" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E231" s="12">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B232" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C232" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D232" s="4"/>
-      <c r="E232" s="9"/>
-    </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D232" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E232" s="12">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="233" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B233" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D233" s="4"/>
-      <c r="E233" s="9"/>
-    </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D233" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E233" s="12">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5" ht="67.2" x14ac:dyDescent="0.3">
       <c r="B234" s="8" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C234" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D234" s="4"/>
-      <c r="E234" s="9"/>
-    </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D234" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E234" s="12">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="235" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B235" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C235" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D235" s="4"/>
-      <c r="E235" s="9"/>
-    </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D235" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E235" s="12">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="236" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B236" s="8" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C236" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D236" s="4"/>
-      <c r="E236" s="9"/>
-    </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D236" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E236" s="12">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="237" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B237" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D237" s="4"/>
-      <c r="E237" s="9"/>
+      <c r="D237" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E237" s="12">
+        <v>2018</v>
+      </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B238" s="8" t="s">
@@ -6778,9 +6897,23 @@
     <hyperlink ref="E222" r:id="rId98" display="https://myanimelist.net/manga/120130/Nijusseiki_Denki_Mokuroku" xr:uid="{4A9D79AB-AB69-48EB-8C88-712B2769910B}"/>
     <hyperlink ref="E223" r:id="rId99" display="https://myanimelist.net/manga/144353/Neko_to_Ryuu" xr:uid="{944AF126-B106-4C12-9363-E84E8B95FB74}"/>
     <hyperlink ref="E94" r:id="rId100" display="https://myanimelist.net/manga/92594/Momokuri" xr:uid="{BF93A3FC-0A7D-4BB9-8911-8480518C2C86}"/>
+    <hyperlink ref="E225" r:id="rId101" display="https://myanimelist.net/anime/8425/Gosick" xr:uid="{DE19D9B9-C439-4DCB-87B7-8812776FB40F}"/>
+    <hyperlink ref="E226" r:id="rId102" display="https://myanimelist.net/anime/60531/Bukiyou_na_Senpai" xr:uid="{5445C061-890A-4EE3-A9E6-CE780DDB5EEB}"/>
+    <hyperlink ref="E227" r:id="rId103" display="https://myanimelist.net/manga/116808/Giji_Harem" xr:uid="{7EBF3155-2134-4E4B-A9C4-74A3A480331F}"/>
+    <hyperlink ref="E228" r:id="rId104" display="https://myanimelist.net/manga/118196/Kawaii_dake_ja_Nai_Shikimori-san" xr:uid="{9D2D2C98-3486-48EF-A8B8-371B03BDBA27}"/>
+    <hyperlink ref="E229" r:id="rId105" display="https://myanimelist.net/anime/52990/Keikenzumi_na_Kimi_to_Keiken_Zero_na_Ore_ga_Otsukiai_suru_Hanashi" xr:uid="{5EE62E1D-1B8B-4377-B278-1445A77CCAE9}"/>
+    <hyperlink ref="E230" r:id="rId106" display="https://myanimelist.net/manga/81211/Shuumatsu_Nani_Shitemasu_ka_Isogashii_desu_ka_Sukutte_Moratte_Ii_desu_ka" xr:uid="{90DAA255-CC43-4FA2-8C41-891B2A8D51AE}"/>
+    <hyperlink ref="E231" r:id="rId107" display="https://myanimelist.net/anime/56923/Lv2_kara_Cheat_datta_Motoyuusha_Kouho_no_Mattari_Isekai_Life" xr:uid="{42E19880-65F5-4D9D-A604-9C37F15087F6}"/>
+    <hyperlink ref="E232" r:id="rId108" display="https://myanimelist.net/manga/170020/Kami_no_Niwatsuki_Kusunoki-tei" xr:uid="{A64EE46F-4EC1-41A5-9AB3-D810F9D7C94C}"/>
+    <hyperlink ref="E233" r:id="rId109" display="https://myanimelist.net/anime/52173/Koori_Zokusei_Danshi_to_Cool_na_Douryou_Joshi" xr:uid="{CCE5BB37-2F77-45A8-803A-0BE50B94DA6F}"/>
+    <hyperlink ref="E182" r:id="rId110" display="https://myanimelist.net/anime/33487/Masamune-kun_no_Revenge" xr:uid="{D2BE633A-8F78-4106-B831-1532C4C4331B}"/>
+    <hyperlink ref="E234" r:id="rId111" display="https://myanimelist.net/manga/116772/Kono_Yuusha_ga_Ore_Tueee_Kuse_ni_Shinchou_sugiru" xr:uid="{F2C49E0D-9037-43E0-804A-9D812D8BC04D}"/>
+    <hyperlink ref="E235" r:id="rId112" display="https://myanimelist.net/anime/51614/Ao_no_Orchestra" xr:uid="{3039ED1F-017C-4892-B252-C24EC904420E}"/>
+    <hyperlink ref="E236" r:id="rId113" display="https://myanimelist.net/manga/86337/Black_Clover" xr:uid="{C25449AB-F9EB-4B32-BAAE-7D33B4D8B5C3}"/>
+    <hyperlink ref="E237" r:id="rId114" display="https://myanimelist.net/manga/120130/Nijusseiki_Denki_Mokuroku" xr:uid="{DCD2A396-FE61-409F-A6AB-F50558CF90E7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId101"/>
-  <drawing r:id="rId102"/>
+  <pageSetup orientation="portrait" r:id="rId115"/>
+  <drawing r:id="rId116"/>
 </worksheet>
 </file>
--- a/fullanime.xlsx
+++ b/fullanime.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VoVanLinhTinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65523C51-A729-4547-A8AA-94675AE2D9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB123B64-A46B-4F70-A205-06734964E8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="253">
   <si>
     <t>Netoge no Yome ga Ninki Idol datta</t>
   </si>
@@ -1227,6 +1227,21 @@
     <t>Nijusseiki Denki Mokuroku
 二十世紀電氣目録
 Danh mục thiết bị điện thế kỷ 20</t>
+  </si>
+  <si>
+    <t>Kao ni Denai Kashiwada-san to Kao ni Deru Oota-kun
+顔に出ない柏田さんと顔に出る太田君
+Kashiwada-san không thể hiện cảm xúc của mình, trong khi Ota-kun thì có</t>
+  </si>
+  <si>
+    <t>Sekai Saikou no Ansatsusha, Isekai Kizoku ni Tensei suru
+世界最高の暗殺者、異世界貴族に転生する
+Sát thủ vĩ đại nhất thế giới được tái sinh thành một quý tộc ở một thế giới khác</t>
+  </si>
+  <si>
+    <t>Hotaru no Yomeiri
+ホタルの嫁入り
+Đám cưới đom đóm</t>
   </si>
 </sst>
 </file>
@@ -4951,10 +4966,10 @@
     </row>
     <row r="236" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B236" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>248</v>
@@ -4977,35 +4992,47 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B238" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C238" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D238" s="4"/>
-      <c r="E238" s="9"/>
-    </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D238" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E238" s="12">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="239" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B239" s="8" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C239" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D239" s="4"/>
-      <c r="E239" s="9"/>
-    </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D239" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E239" s="12">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="240" spans="2:5" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B240" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D240" s="4"/>
-      <c r="E240" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E240" s="12">
+        <v>2023</v>
+      </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B241" s="8" t="s">
@@ -6911,9 +6938,12 @@
     <hyperlink ref="E235" r:id="rId112" display="https://myanimelist.net/anime/51614/Ao_no_Orchestra" xr:uid="{3039ED1F-017C-4892-B252-C24EC904420E}"/>
     <hyperlink ref="E236" r:id="rId113" display="https://myanimelist.net/manga/86337/Black_Clover" xr:uid="{C25449AB-F9EB-4B32-BAAE-7D33B4D8B5C3}"/>
     <hyperlink ref="E237" r:id="rId114" display="https://myanimelist.net/manga/120130/Nijusseiki_Denki_Mokuroku" xr:uid="{DCD2A396-FE61-409F-A6AB-F50558CF90E7}"/>
+    <hyperlink ref="E238" r:id="rId115" display="https://myanimelist.net/manga/115186/Kao_ni_Denai_Kashiwada-san_to_Kao_ni_Deru_Oota-kun" xr:uid="{FA539C1A-F63C-4F42-9771-E012E3EE2EBB}"/>
+    <hyperlink ref="E239" r:id="rId116" display="https://myanimelist.net/manga/120548/Sekai_Saikou_no_Ansatsusha_Isekai_Kizoku_ni_Tensei_suru" xr:uid="{391B6717-D4C6-423C-85E5-862640BD9DEA}"/>
+    <hyperlink ref="E240" r:id="rId117" display="https://myanimelist.net/manga/154679/Hotaru_no_Yomeiri" xr:uid="{FD187578-3CF7-4416-8D4E-D38F161B2CC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId115"/>
-  <drawing r:id="rId116"/>
+  <pageSetup orientation="portrait" r:id="rId118"/>
+  <drawing r:id="rId119"/>
 </worksheet>
 </file>